--- a/assets/images/Epreuve E5 - Tableau de synthese TABIBOU Wassila (4).xlsx
+++ b/assets/images/Epreuve E5 - Tableau de synthese TABIBOU Wassila (4).xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stagiaire\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stagiaire\Documents\Portfolio\assets\images\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14380" windowHeight="4100"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6930"/>
   </bookViews>
   <sheets>
     <sheet name="Tableau de synthèse Épreuve E5" sheetId="1" r:id="rId1"/>
@@ -150,9 +150,6 @@
     <t>Centre de formation : ESIC</t>
   </si>
   <si>
-    <t>Adresse URL du portfolio : https://???</t>
-  </si>
-  <si>
     <t>CoreFlow (Portail Intranet collaboratif)</t>
   </si>
   <si>
@@ -169,6 +166,9 @@
   </si>
   <si>
     <t>Module Paramétrage Envois XLS</t>
+  </si>
+  <si>
+    <t>Adresse URL du portfolio : https://wassilatabibou.github.io/Portfolio/</t>
   </si>
 </sst>
 </file>
@@ -706,15 +706,45 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -747,36 +777,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1221,30 +1221,30 @@
       <c r="H2" s="25"/>
     </row>
     <row r="3" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="37" t="s">
+      <c r="A3" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="43" t="s">
-        <v>33</v>
-      </c>
-      <c r="G3" s="38"/>
-      <c r="H3" s="44"/>
+      <c r="G3" s="27"/>
+      <c r="H3" s="33"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="40" t="s">
+      <c r="A4" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="41"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="42"/>
+      <c r="B4" s="30"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="31"/>
       <c r="F4" s="12" t="s">
         <v>3</v>
       </c>
@@ -1256,22 +1256,22 @@
       </c>
     </row>
     <row r="5" spans="1:43" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="34" t="s">
-        <v>30</v>
-      </c>
-      <c r="B5" s="35"/>
-      <c r="C5" s="35"/>
-      <c r="D5" s="35"/>
-      <c r="E5" s="35"/>
-      <c r="F5" s="35"/>
-      <c r="G5" s="35"/>
-      <c r="H5" s="36"/>
+      <c r="A5" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="45"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="46"/>
     </row>
     <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="32" t="s">
+      <c r="B6" s="42" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="6" t="s">
@@ -1294,8 +1294,8 @@
       </c>
     </row>
     <row r="7" spans="1:43" s="2" customFormat="1" ht="324.89999999999998" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="24"/>
-      <c r="B7" s="33"/>
+      <c r="A7" s="35"/>
+      <c r="B7" s="43"/>
       <c r="C7" s="19" t="s">
         <v>14</v>
       </c>
@@ -1351,16 +1351,16 @@
       <c r="AQ7"/>
     </row>
     <row r="8" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.25">
-      <c r="A8" s="26" t="s">
+      <c r="A8" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="27"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27"/>
-      <c r="H8" s="28"/>
+      <c r="B8" s="37"/>
+      <c r="C8" s="37"/>
+      <c r="D8" s="37"/>
+      <c r="E8" s="37"/>
+      <c r="F8" s="37"/>
+      <c r="G8" s="37"/>
+      <c r="H8" s="38"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1399,7 +1399,7 @@
     </row>
     <row r="9" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
@@ -1894,16 +1894,16 @@
       <c r="AQ18"/>
     </row>
     <row r="19" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.25">
-      <c r="A19" s="29" t="s">
+      <c r="A19" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="30"/>
-      <c r="C19" s="30"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="30"/>
-      <c r="H19" s="31"/>
+      <c r="B19" s="40"/>
+      <c r="C19" s="40"/>
+      <c r="D19" s="40"/>
+      <c r="E19" s="40"/>
+      <c r="F19" s="40"/>
+      <c r="G19" s="40"/>
+      <c r="H19" s="41"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -1942,9 +1942,9 @@
     </row>
     <row r="20" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B20" s="46">
+        <v>35</v>
+      </c>
+      <c r="B20" s="24">
         <v>2025</v>
       </c>
       <c r="C20" s="14" t="s">
@@ -2270,16 +2270,16 @@
       <c r="AQ26"/>
     </row>
     <row r="27" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.25">
-      <c r="A27" s="29" t="s">
+      <c r="A27" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="B27" s="30"/>
-      <c r="C27" s="30"/>
-      <c r="D27" s="30"/>
-      <c r="E27" s="30"/>
-      <c r="F27" s="30"/>
-      <c r="G27" s="30"/>
-      <c r="H27" s="31"/>
+      <c r="B27" s="40"/>
+      <c r="C27" s="40"/>
+      <c r="D27" s="40"/>
+      <c r="E27" s="40"/>
+      <c r="F27" s="40"/>
+      <c r="G27" s="40"/>
+      <c r="H27" s="41"/>
       <c r="I27"/>
       <c r="J27"/>
       <c r="K27"/>
@@ -2318,7 +2318,7 @@
     </row>
     <row r="28" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B28" s="22" t="s">
         <v>27</v>
@@ -2379,7 +2379,7 @@
     </row>
     <row r="29" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B29" s="22" t="s">
         <v>27</v>
@@ -2438,9 +2438,9 @@
     </row>
     <row r="30" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B30" s="45" t="s">
+        <v>35</v>
+      </c>
+      <c r="B30" s="23" t="s">
         <v>27</v>
       </c>
       <c r="C30" s="14" t="s">
@@ -2768,11 +2768,6 @@
     <row r="81" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A8:H8"/>
@@ -2780,6 +2775,11 @@
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A5:H5"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -2809,18 +2809,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="d4baab8d-1d27-44c4-8784-fbcb6b3058ce" xsi:nil="true"/>
-    <Date xmlns="9da37709-037e-454b-bc61-0f9e6296192f" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9da37709-037e-454b-bc61-0f9e6296192f">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100EC12EF1C0A58B54688C58C6681402A50" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c746cb13fd9d5a7189a1c28d57eb3a86">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9da37709-037e-454b-bc61-0f9e6296192f" xmlns:ns3="d4baab8d-1d27-44c4-8784-fbcb6b3058ce" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="45c00262109c5c4f60d5c80d45812836" ns2:_="" ns3:_="">
     <xsd:import namespace="9da37709-037e-454b-bc61-0f9e6296192f"/>
@@ -3027,6 +3015,18 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="d4baab8d-1d27-44c4-8784-fbcb6b3058ce" xsi:nil="true"/>
+    <Date xmlns="9da37709-037e-454b-bc61-0f9e6296192f" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9da37709-037e-454b-bc61-0f9e6296192f">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5E86901B-5A84-4956-8164-795728FD1A91}">
   <ds:schemaRefs>
@@ -3036,17 +3036,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69C890D7-805D-4AFB-9A4E-D03A02689D48}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d4baab8d-1d27-44c4-8784-fbcb6b3058ce"/>
-    <ds:schemaRef ds:uri="9da37709-037e-454b-bc61-0f9e6296192f"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6670BDA6-576F-4CB3-91FF-2C91CBE33E0F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3063,4 +3052,15 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69C890D7-805D-4AFB-9A4E-D03A02689D48}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d4baab8d-1d27-44c4-8784-fbcb6b3058ce"/>
+    <ds:schemaRef ds:uri="9da37709-037e-454b-bc61-0f9e6296192f"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/assets/images/Epreuve E5 - Tableau de synthese TABIBOU Wassila (4).xlsx
+++ b/assets/images/Epreuve E5 - Tableau de synthese TABIBOU Wassila (4).xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="36">
   <si>
     <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
   </si>
@@ -133,9 +133,6 @@
   </si>
   <si>
     <t>Application de gestion de réservations (Salles et Matériel)</t>
-  </si>
-  <si>
-    <t>FreedomMoney (Gestion bancaire)</t>
   </si>
   <si>
     <t>GameHub (Collection jeux vidéo)</t>
@@ -712,9 +709,48 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -737,45 +773,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1195,56 +1192,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25" t="s">
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="25"/>
+      <c r="H1" s="27"/>
     </row>
     <row r="2" spans="1:43" ht="41.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
     </row>
     <row r="3" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="26" t="s">
+      <c r="A3" s="39" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="40"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="27"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="32" t="s">
-        <v>32</v>
-      </c>
-      <c r="G3" s="27"/>
-      <c r="H3" s="33"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="46"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="29" t="s">
-        <v>29</v>
-      </c>
-      <c r="B4" s="30"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="31"/>
+      <c r="A4" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="43"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="44"/>
       <c r="F4" s="12" t="s">
         <v>3</v>
       </c>
@@ -1256,22 +1253,22 @@
       </c>
     </row>
     <row r="5" spans="1:43" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="B5" s="45"/>
-      <c r="C5" s="45"/>
-      <c r="D5" s="45"/>
-      <c r="E5" s="45"/>
-      <c r="F5" s="45"/>
-      <c r="G5" s="45"/>
-      <c r="H5" s="46"/>
+      <c r="A5" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="37"/>
+      <c r="C5" s="37"/>
+      <c r="D5" s="37"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="37"/>
+      <c r="G5" s="37"/>
+      <c r="H5" s="38"/>
     </row>
     <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="34" t="s">
+      <c r="A6" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="42" t="s">
+      <c r="B6" s="34" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="6" t="s">
@@ -1294,8 +1291,8 @@
       </c>
     </row>
     <row r="7" spans="1:43" s="2" customFormat="1" ht="324.89999999999998" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="35"/>
-      <c r="B7" s="43"/>
+      <c r="A7" s="26"/>
+      <c r="B7" s="35"/>
       <c r="C7" s="19" t="s">
         <v>14</v>
       </c>
@@ -1351,16 +1348,16 @@
       <c r="AQ7"/>
     </row>
     <row r="8" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.25">
-      <c r="A8" s="36" t="s">
+      <c r="A8" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="37"/>
-      <c r="C8" s="37"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="37"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="37"/>
-      <c r="H8" s="38"/>
+      <c r="B8" s="29"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="29"/>
+      <c r="H8" s="30"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1399,10 +1396,10 @@
     </row>
     <row r="9" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C9" s="14" t="s">
         <v>23</v>
@@ -1461,7 +1458,7 @@
         <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C10" s="14" t="s">
         <v>23</v>
@@ -1516,7 +1513,7 @@
         <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C11" s="14" t="s">
         <v>23</v>
@@ -1529,9 +1526,7 @@
       <c r="G11" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="H11" s="15" t="s">
-        <v>23</v>
-      </c>
+      <c r="H11" s="15"/>
       <c r="I11"/>
       <c r="J11"/>
       <c r="K11"/>
@@ -1569,23 +1564,13 @@
       <c r="AQ11"/>
     </row>
     <row r="12" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" s="14" t="s">
-        <v>23</v>
-      </c>
+      <c r="A12" s="9"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="14"/>
       <c r="D12" s="14"/>
       <c r="E12" s="14"/>
-      <c r="F12" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="G12" s="14" t="s">
-        <v>23</v>
-      </c>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
       <c r="H12" s="15"/>
       <c r="I12"/>
       <c r="J12"/>
@@ -1894,16 +1879,16 @@
       <c r="AQ18"/>
     </row>
     <row r="19" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.25">
-      <c r="A19" s="39" t="s">
+      <c r="A19" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="40"/>
-      <c r="C19" s="40"/>
-      <c r="D19" s="40"/>
-      <c r="E19" s="40"/>
-      <c r="F19" s="40"/>
-      <c r="G19" s="40"/>
-      <c r="H19" s="41"/>
+      <c r="B19" s="32"/>
+      <c r="C19" s="32"/>
+      <c r="D19" s="32"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="32"/>
+      <c r="H19" s="33"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -1942,7 +1927,7 @@
     </row>
     <row r="20" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B20" s="24">
         <v>2025</v>
@@ -2270,16 +2255,16 @@
       <c r="AQ26"/>
     </row>
     <row r="27" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.25">
-      <c r="A27" s="39" t="s">
+      <c r="A27" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="B27" s="40"/>
-      <c r="C27" s="40"/>
-      <c r="D27" s="40"/>
-      <c r="E27" s="40"/>
-      <c r="F27" s="40"/>
-      <c r="G27" s="40"/>
-      <c r="H27" s="41"/>
+      <c r="B27" s="32"/>
+      <c r="C27" s="32"/>
+      <c r="D27" s="32"/>
+      <c r="E27" s="32"/>
+      <c r="F27" s="32"/>
+      <c r="G27" s="32"/>
+      <c r="H27" s="33"/>
       <c r="I27"/>
       <c r="J27"/>
       <c r="K27"/>
@@ -2318,10 +2303,10 @@
     </row>
     <row r="28" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B28" s="22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C28" s="14" t="s">
         <v>23</v>
@@ -2379,10 +2364,10 @@
     </row>
     <row r="29" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B29" s="22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C29" s="14" t="s">
         <v>23</v>
@@ -2438,10 +2423,10 @@
     </row>
     <row r="30" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B30" s="23" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C30" s="14" t="s">
         <v>23</v>
@@ -2768,6 +2753,11 @@
     <row r="81" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A8:H8"/>
@@ -2775,11 +2765,6 @@
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A5:H5"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -2800,15 +2785,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100EC12EF1C0A58B54688C58C6681402A50" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c746cb13fd9d5a7189a1c28d57eb3a86">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9da37709-037e-454b-bc61-0f9e6296192f" xmlns:ns3="d4baab8d-1d27-44c4-8784-fbcb6b3058ce" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="45c00262109c5c4f60d5c80d45812836" ns2:_="" ns3:_="">
     <xsd:import namespace="9da37709-037e-454b-bc61-0f9e6296192f"/>
@@ -3015,6 +2991,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -3028,14 +3013,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5E86901B-5A84-4956-8164-795728FD1A91}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6670BDA6-576F-4CB3-91FF-2C91CBE33E0F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3054,13 +3031,27 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5E86901B-5A84-4956-8164-795728FD1A91}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69C890D7-805D-4AFB-9A4E-D03A02689D48}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="9da37709-037e-454b-bc61-0f9e6296192f"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="d4baab8d-1d27-44c4-8784-fbcb6b3058ce"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d4baab8d-1d27-44c4-8784-fbcb6b3058ce"/>
-    <ds:schemaRef ds:uri="9da37709-037e-454b-bc61-0f9e6296192f"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>